--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/before_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/before_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Weixi–Qiaohou Fault</t>
@@ -500,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AE53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="21.7109375" customWidth="1"/>
@@ -528,9 +531,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,13 +625,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>26.4357</v>
@@ -675,12 +682,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>26.4357</v>
@@ -728,12 +735,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>26.4357</v>
@@ -781,12 +788,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>26.4357</v>
@@ -846,12 +853,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>26.2537</v>
@@ -899,12 +906,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>26.2537</v>
@@ -949,12 +956,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>26.2537</v>
@@ -1002,12 +1009,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>26.2537</v>
@@ -1055,12 +1062,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>26.2537</v>
@@ -1108,12 +1115,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>26.2537</v>
@@ -1161,12 +1168,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>26.2537</v>
@@ -1223,12 +1230,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>26.2519</v>
@@ -1276,12 +1283,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>26.2519</v>
@@ -1329,12 +1336,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>26.2519</v>
@@ -1382,12 +1389,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>26.2519</v>
@@ -1449,10 +1456,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17">
         <v>26.2392</v>
@@ -1499,10 +1506,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>26.2392</v>
@@ -1552,10 +1559,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>26.2392</v>
@@ -1605,10 +1612,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>26.2392</v>
@@ -1658,10 +1665,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21">
         <v>26.2392</v>
@@ -1711,10 +1718,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22">
         <v>26.2392</v>
@@ -1764,10 +1771,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>26.2392</v>
@@ -1829,10 +1836,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>26.0843</v>
@@ -1879,10 +1886,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25">
         <v>26.0843</v>
@@ -1932,10 +1939,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26">
         <v>26.0843</v>
@@ -1985,10 +1992,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27">
         <v>26.0843</v>
@@ -2038,10 +2045,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>26.0843</v>
@@ -2103,10 +2110,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>25.8047</v>
@@ -2156,10 +2163,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>25.8047</v>
@@ -2209,10 +2216,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>25.8047</v>
@@ -2262,10 +2269,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>25.8047</v>
@@ -2315,10 +2322,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33">
         <v>25.8047</v>
@@ -2368,10 +2375,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34">
         <v>25.8047</v>
@@ -2433,10 +2440,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35">
         <v>25.5697</v>
@@ -2483,10 +2490,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>25.5697</v>
@@ -2536,10 +2543,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C37">
         <v>25.5697</v>
@@ -2589,10 +2596,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C38">
         <v>25.5697</v>
@@ -2642,10 +2649,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C39">
         <v>25.5697</v>
@@ -2695,10 +2702,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>25.5697</v>
@@ -2760,10 +2767,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41">
         <v>25.5697</v>
@@ -2813,10 +2820,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C42">
         <v>25.5621</v>
@@ -2866,10 +2873,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>3.87</v>
@@ -2907,10 +2914,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C44">
         <v>3.85</v>
@@ -2948,10 +2955,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C45">
         <v>3.45</v>
@@ -2989,10 +2996,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C46">
         <v>3.45</v>
@@ -3054,10 +3061,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C47">
         <v>25.1706</v>
@@ -3104,10 +3111,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C48">
         <v>25.1706</v>
@@ -3154,10 +3161,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C49">
         <v>25.1706</v>
@@ -3207,10 +3214,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C50">
         <v>25.1706</v>
@@ -3260,10 +3267,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C51">
         <v>25.1706</v>
@@ -3313,10 +3320,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C52">
         <v>25.1706</v>
@@ -3378,10 +3385,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N53">
         <v>99.79040000000001</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/before_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/before_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="43">
   <si>
     <t>location</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>XQC</t>
+  </si>
+  <si>
+    <t>Metamorphic Rock</t>
   </si>
 </sst>
 </file>
@@ -510,7 +513,7 @@
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -642,6 +645,9 @@
       <c r="D2">
         <v>99.6268</v>
       </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
       <c r="H2">
         <v>34</v>
       </c>
@@ -695,6 +701,9 @@
       <c r="D3">
         <v>99.6268</v>
       </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
       <c r="H3">
         <v>34</v>
       </c>
@@ -748,6 +757,9 @@
       <c r="D4">
         <v>99.6268</v>
       </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
       <c r="H4">
         <v>34</v>
       </c>
@@ -801,6 +813,9 @@
       <c r="D5">
         <v>99.6268</v>
       </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
       <c r="H5">
         <v>34</v>
       </c>
@@ -866,6 +881,9 @@
       <c r="D6">
         <v>99.9877</v>
       </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
       <c r="H6">
         <v>78</v>
       </c>
@@ -919,6 +937,9 @@
       <c r="D7">
         <v>99.9877</v>
       </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
       <c r="H7">
         <v>78</v>
       </c>
@@ -969,6 +990,9 @@
       <c r="D8">
         <v>99.9877</v>
       </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
       <c r="H8">
         <v>78</v>
       </c>
@@ -1022,6 +1046,9 @@
       <c r="D9">
         <v>99.9877</v>
       </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
       <c r="H9">
         <v>78</v>
       </c>
@@ -1075,6 +1102,9 @@
       <c r="D10">
         <v>99.9877</v>
       </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
       <c r="H10">
         <v>78</v>
       </c>
@@ -1128,6 +1158,9 @@
       <c r="D11">
         <v>99.9877</v>
       </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
       <c r="H11">
         <v>78</v>
       </c>
@@ -1181,6 +1214,9 @@
       <c r="D12">
         <v>99.9877</v>
       </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
       <c r="H12">
         <v>78</v>
       </c>
@@ -1243,6 +1279,9 @@
       <c r="D13">
         <v>99.9913</v>
       </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
       <c r="H13">
         <v>72</v>
       </c>
@@ -1296,6 +1335,9 @@
       <c r="D14">
         <v>99.9913</v>
       </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
       <c r="H14">
         <v>72</v>
       </c>
@@ -1349,6 +1391,9 @@
       <c r="D15">
         <v>99.9913</v>
       </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
       <c r="H15">
         <v>72</v>
       </c>
@@ -1402,6 +1447,9 @@
       <c r="D16">
         <v>99.9913</v>
       </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
       <c r="H16">
         <v>72</v>
       </c>
@@ -1467,6 +1515,9 @@
       <c r="D17">
         <v>99.9926</v>
       </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
       <c r="H17">
         <v>74</v>
       </c>
@@ -1517,6 +1568,9 @@
       <c r="D18">
         <v>99.9926</v>
       </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
       <c r="H18">
         <v>74</v>
       </c>
@@ -1570,6 +1624,9 @@
       <c r="D19">
         <v>99.9926</v>
       </c>
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
       <c r="H19">
         <v>74</v>
       </c>
@@ -1623,6 +1680,9 @@
       <c r="D20">
         <v>99.9926</v>
       </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
       <c r="H20">
         <v>74</v>
       </c>
@@ -1676,6 +1736,9 @@
       <c r="D21">
         <v>99.9926</v>
       </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
       <c r="H21">
         <v>74</v>
       </c>
@@ -1729,6 +1792,9 @@
       <c r="D22">
         <v>99.9926</v>
       </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
       <c r="H22">
         <v>74</v>
       </c>
@@ -1782,6 +1848,9 @@
       <c r="D23">
         <v>99.9926</v>
       </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
       <c r="H23">
         <v>74</v>
       </c>
@@ -1847,6 +1916,9 @@
       <c r="D24">
         <v>100.0252</v>
       </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
       <c r="H24">
         <v>92</v>
       </c>
@@ -1897,6 +1969,9 @@
       <c r="D25">
         <v>100.0252</v>
       </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
       <c r="H25">
         <v>92</v>
       </c>
@@ -1950,6 +2025,9 @@
       <c r="D26">
         <v>100.0252</v>
       </c>
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
       <c r="H26">
         <v>92</v>
       </c>
@@ -2003,6 +2081,9 @@
       <c r="D27">
         <v>100.0252</v>
       </c>
+      <c r="F27" t="s">
+        <v>42</v>
+      </c>
       <c r="H27">
         <v>92</v>
       </c>
@@ -2056,6 +2137,9 @@
       <c r="D28">
         <v>100.0252</v>
       </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
       <c r="H28">
         <v>92</v>
       </c>
@@ -2121,6 +2205,9 @@
       <c r="D29">
         <v>99.9204</v>
       </c>
+      <c r="F29" t="s">
+        <v>42</v>
+      </c>
       <c r="H29">
         <v>70</v>
       </c>
@@ -2174,6 +2261,9 @@
       <c r="D30">
         <v>99.9204</v>
       </c>
+      <c r="F30" t="s">
+        <v>42</v>
+      </c>
       <c r="H30">
         <v>70</v>
       </c>
@@ -2227,6 +2317,9 @@
       <c r="D31">
         <v>99.9204</v>
       </c>
+      <c r="F31" t="s">
+        <v>42</v>
+      </c>
       <c r="H31">
         <v>70</v>
       </c>
@@ -2280,6 +2373,9 @@
       <c r="D32">
         <v>99.9204</v>
       </c>
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
       <c r="H32">
         <v>70</v>
       </c>
@@ -2333,6 +2429,9 @@
       <c r="D33">
         <v>99.9204</v>
       </c>
+      <c r="F33" t="s">
+        <v>42</v>
+      </c>
       <c r="H33">
         <v>70</v>
       </c>
@@ -2386,6 +2485,9 @@
       <c r="D34">
         <v>99.9204</v>
       </c>
+      <c r="F34" t="s">
+        <v>42</v>
+      </c>
       <c r="H34">
         <v>70</v>
       </c>
@@ -2451,6 +2553,9 @@
       <c r="D35">
         <v>100.1822</v>
       </c>
+      <c r="F35" t="s">
+        <v>42</v>
+      </c>
       <c r="H35">
         <v>78</v>
       </c>
@@ -2501,6 +2606,9 @@
       <c r="D36">
         <v>100.1822</v>
       </c>
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
       <c r="H36">
         <v>78</v>
       </c>
@@ -2554,6 +2662,9 @@
       <c r="D37">
         <v>100.1822</v>
       </c>
+      <c r="F37" t="s">
+        <v>42</v>
+      </c>
       <c r="H37">
         <v>78</v>
       </c>
@@ -2607,6 +2718,9 @@
       <c r="D38">
         <v>100.1822</v>
       </c>
+      <c r="F38" t="s">
+        <v>42</v>
+      </c>
       <c r="H38">
         <v>78</v>
       </c>
@@ -2660,6 +2774,9 @@
       <c r="D39">
         <v>100.1822</v>
       </c>
+      <c r="F39" t="s">
+        <v>42</v>
+      </c>
       <c r="H39">
         <v>78</v>
       </c>
@@ -2713,6 +2830,9 @@
       <c r="D40">
         <v>100.1822</v>
       </c>
+      <c r="F40" t="s">
+        <v>42</v>
+      </c>
       <c r="H40">
         <v>78</v>
       </c>
@@ -2778,6 +2898,9 @@
       <c r="D41">
         <v>100.1822</v>
       </c>
+      <c r="F41" t="s">
+        <v>42</v>
+      </c>
       <c r="H41">
         <v>78</v>
       </c>
@@ -2831,6 +2954,9 @@
       <c r="D42">
         <v>100.1299</v>
       </c>
+      <c r="F42" t="s">
+        <v>42</v>
+      </c>
       <c r="H42">
         <v>63</v>
       </c>
@@ -2884,6 +3010,9 @@
       <c r="D43">
         <v>92.16</v>
       </c>
+      <c r="F43" t="s">
+        <v>42</v>
+      </c>
       <c r="H43">
         <v>1</v>
       </c>
@@ -2925,6 +3054,9 @@
       <c r="D44">
         <v>96.59999999999999</v>
       </c>
+      <c r="F44" t="s">
+        <v>42</v>
+      </c>
       <c r="H44">
         <v>0.99</v>
       </c>
@@ -2966,6 +3098,9 @@
       <c r="D45">
         <v>92.95999999999999</v>
       </c>
+      <c r="F45" t="s">
+        <v>42</v>
+      </c>
       <c r="H45">
         <v>1.07</v>
       </c>
@@ -3007,6 +3142,9 @@
       <c r="D46">
         <v>92.95999999999999</v>
       </c>
+      <c r="F46" t="s">
+        <v>42</v>
+      </c>
       <c r="H46">
         <v>1.07</v>
       </c>
@@ -3072,6 +3210,9 @@
       <c r="D47">
         <v>100.323</v>
       </c>
+      <c r="F47" t="s">
+        <v>42</v>
+      </c>
       <c r="H47">
         <v>46</v>
       </c>
@@ -3122,6 +3263,9 @@
       <c r="D48">
         <v>100.323</v>
       </c>
+      <c r="F48" t="s">
+        <v>42</v>
+      </c>
       <c r="H48">
         <v>46</v>
       </c>
@@ -3172,6 +3316,9 @@
       <c r="D49">
         <v>100.323</v>
       </c>
+      <c r="F49" t="s">
+        <v>42</v>
+      </c>
       <c r="H49">
         <v>46</v>
       </c>
@@ -3225,6 +3372,9 @@
       <c r="D50">
         <v>100.323</v>
       </c>
+      <c r="F50" t="s">
+        <v>42</v>
+      </c>
       <c r="H50">
         <v>46</v>
       </c>
@@ -3278,6 +3428,9 @@
       <c r="D51">
         <v>100.323</v>
       </c>
+      <c r="F51" t="s">
+        <v>42</v>
+      </c>
       <c r="H51">
         <v>46</v>
       </c>
@@ -3331,6 +3484,9 @@
       <c r="D52">
         <v>100.323</v>
       </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
       <c r="H52">
         <v>46</v>
       </c>
@@ -3389,6 +3545,9 @@
       </c>
       <c r="B53" t="s">
         <v>41</v>
+      </c>
+      <c r="F53" t="s">
+        <v>42</v>
       </c>
       <c r="N53">
         <v>99.79040000000001</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/before_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/before_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -517,7 +517,7 @@
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="23.7109375" customWidth="1"/>
     <col min="12" max="12" width="34.7109375" customWidth="1"/>
     <col min="13" max="17" width="14.7109375" customWidth="1"/>
@@ -909,7 +909,7 @@
         <v>151.68</v>
       </c>
       <c r="S6">
-        <v>0.708718</v>
+        <v>627.8200000000001</v>
       </c>
       <c r="U6">
         <v>34.8</v>
@@ -962,7 +962,10 @@
         <v>14.93</v>
       </c>
       <c r="R7">
-        <v>4.31</v>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>580.66</v>
       </c>
       <c r="U7">
         <v>8.699999999999999</v>
@@ -971,7 +974,7 @@
         <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD7">
         <v>1</v>
@@ -1241,6 +1244,9 @@
       <c r="R12">
         <v>149.8</v>
       </c>
+      <c r="S12">
+        <v>640.22</v>
+      </c>
       <c r="T12">
         <v>1.145</v>
       </c>
@@ -1542,6 +1548,9 @@
       <c r="R17">
         <v>210.18</v>
       </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
       <c r="U17">
         <v>44.3</v>
       </c>
@@ -1549,7 +1558,7 @@
         <v>6.8</v>
       </c>
       <c r="AA17">
-        <v>0.708887</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <v>1</v>
@@ -1943,6 +1952,9 @@
       <c r="R24">
         <v>238.91</v>
       </c>
+      <c r="S24">
+        <v>241.23</v>
+      </c>
       <c r="U24">
         <v>17.9</v>
       </c>
@@ -1950,7 +1962,7 @@
         <v>6.82</v>
       </c>
       <c r="AA24">
-        <v>241.23</v>
+        <v>0</v>
       </c>
       <c r="AD24">
         <v>1</v>
@@ -2580,6 +2592,9 @@
       <c r="R35">
         <v>304.79</v>
       </c>
+      <c r="S35">
+        <v>556.6900000000001</v>
+      </c>
       <c r="U35">
         <v>18.76</v>
       </c>
@@ -2587,7 +2602,7 @@
         <v>6.71</v>
       </c>
       <c r="AA35">
-        <v>556.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="AD35">
         <v>1</v>
@@ -3005,37 +3020,49 @@
         <v>39</v>
       </c>
       <c r="C43">
+        <v>25.5621</v>
+      </c>
+      <c r="D43">
+        <v>100.1299</v>
+      </c>
+      <c r="F43" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43">
+        <v>63</v>
+      </c>
+      <c r="I43">
+        <v>471</v>
+      </c>
+      <c r="J43">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="N43">
+        <v>92.16</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43">
+        <v>10.98</v>
+      </c>
+      <c r="Q43">
+        <v>4.31</v>
+      </c>
+      <c r="R43">
+        <v>84.44</v>
+      </c>
+      <c r="S43">
+        <v>155.96</v>
+      </c>
+      <c r="U43">
         <v>3.87</v>
       </c>
-      <c r="D43">
-        <v>92.16</v>
-      </c>
-      <c r="F43" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43">
+      <c r="Z43">
         <v>5.19</v>
       </c>
-      <c r="J43">
-        <v>10.98</v>
-      </c>
-      <c r="N43">
-        <v>4.31</v>
-      </c>
-      <c r="O43">
+      <c r="AA43">
         <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>84.44</v>
-      </c>
-      <c r="Z43">
-        <v>155.96</v>
       </c>
       <c r="AD43">
         <v>1</v>
@@ -3049,37 +3076,49 @@
         <v>39</v>
       </c>
       <c r="C44">
+        <v>25.5621</v>
+      </c>
+      <c r="D44">
+        <v>100.1299</v>
+      </c>
+      <c r="F44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44">
+        <v>63</v>
+      </c>
+      <c r="I44">
+        <v>471</v>
+      </c>
+      <c r="J44">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="N44">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="O44">
+        <v>0.99</v>
+      </c>
+      <c r="P44">
+        <v>12.93</v>
+      </c>
+      <c r="Q44">
+        <v>3.76</v>
+      </c>
+      <c r="R44">
+        <v>82.89</v>
+      </c>
+      <c r="S44">
+        <v>186.54</v>
+      </c>
+      <c r="U44">
         <v>3.85</v>
       </c>
-      <c r="D44">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="F44" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44">
-        <v>0.99</v>
-      </c>
-      <c r="I44">
+      <c r="Z44">
         <v>6.21</v>
       </c>
-      <c r="J44">
-        <v>12.93</v>
-      </c>
-      <c r="N44">
-        <v>3.76</v>
-      </c>
-      <c r="O44">
+      <c r="AA44">
         <v>1.91</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>82.89</v>
-      </c>
-      <c r="Z44">
-        <v>186.54</v>
       </c>
       <c r="AD44">
         <v>1</v>
@@ -3093,37 +3132,49 @@
         <v>39</v>
       </c>
       <c r="C45">
+        <v>25.5621</v>
+      </c>
+      <c r="D45">
+        <v>100.1299</v>
+      </c>
+      <c r="F45" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45">
+        <v>63</v>
+      </c>
+      <c r="I45">
+        <v>471</v>
+      </c>
+      <c r="J45">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="N45">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="O45">
+        <v>1.07</v>
+      </c>
+      <c r="P45">
+        <v>12.63</v>
+      </c>
+      <c r="Q45">
+        <v>3.97</v>
+      </c>
+      <c r="R45">
+        <v>84.7</v>
+      </c>
+      <c r="S45">
+        <v>72.7</v>
+      </c>
+      <c r="U45">
         <v>3.45</v>
       </c>
-      <c r="D45">
-        <v>92.95999999999999</v>
-      </c>
-      <c r="F45" t="s">
-        <v>42</v>
-      </c>
-      <c r="H45">
-        <v>1.07</v>
-      </c>
-      <c r="I45">
+      <c r="Z45">
         <v>5.81</v>
       </c>
-      <c r="J45">
-        <v>12.63</v>
-      </c>
-      <c r="N45">
-        <v>3.97</v>
-      </c>
-      <c r="O45">
+      <c r="AA45">
         <v>0.16</v>
-      </c>
-      <c r="P45">
-        <v>43.32</v>
-      </c>
-      <c r="U45">
-        <v>84.7</v>
-      </c>
-      <c r="Z45">
-        <v>72.7</v>
       </c>
       <c r="AD45">
         <v>1</v>
@@ -3137,22 +3188,22 @@
         <v>39</v>
       </c>
       <c r="C46">
-        <v>3.45</v>
+        <v>25.5621</v>
       </c>
       <c r="D46">
-        <v>92.95999999999999</v>
+        <v>100.1299</v>
       </c>
       <c r="F46" t="s">
         <v>42</v>
       </c>
       <c r="H46">
-        <v>1.07</v>
+        <v>63</v>
       </c>
       <c r="I46">
-        <v>5.81</v>
+        <v>471</v>
       </c>
       <c r="J46">
-        <v>12.63</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N46">
         <v>89.83</v>
@@ -3237,6 +3288,9 @@
       <c r="R47">
         <v>695.64</v>
       </c>
+      <c r="S47">
+        <v>1765.93</v>
+      </c>
       <c r="U47">
         <v>19.18</v>
       </c>
@@ -3244,7 +3298,7 @@
         <v>5.68</v>
       </c>
       <c r="AA47">
-        <v>1765.93</v>
+        <v>0</v>
       </c>
       <c r="AD47">
         <v>1</v>
@@ -3290,6 +3344,9 @@
       <c r="R48">
         <v>719.51</v>
       </c>
+      <c r="S48">
+        <v>1826.65</v>
+      </c>
       <c r="U48">
         <v>19.34</v>
       </c>
@@ -3546,32 +3603,41 @@
       <c r="B53" t="s">
         <v>41</v>
       </c>
+      <c r="C53">
+        <v>25.4829</v>
+      </c>
+      <c r="D53">
+        <v>99.79040000000001</v>
+      </c>
       <c r="F53" t="s">
         <v>42</v>
       </c>
+      <c r="H53">
+        <v>56</v>
+      </c>
       <c r="N53">
-        <v>99.79040000000001</v>
+        <v>151.82</v>
       </c>
       <c r="O53">
-        <v>56</v>
+        <v>9.25</v>
       </c>
       <c r="P53">
-        <v>151.82</v>
+        <v>69.37</v>
       </c>
       <c r="Q53">
-        <v>9.25</v>
+        <v>18.21</v>
       </c>
       <c r="R53">
-        <v>69.37</v>
+        <v>43.84</v>
       </c>
       <c r="S53">
-        <v>43.84</v>
+        <v>603</v>
       </c>
       <c r="T53">
         <v>0.2</v>
       </c>
       <c r="U53">
-        <v>25.4829</v>
+        <v>14.82</v>
       </c>
       <c r="V53">
         <v>12.534</v>
@@ -3583,10 +3649,10 @@
         <v>0.0324</v>
       </c>
       <c r="Z53">
-        <v>14.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="AD53">
         <v>1</v>
